--- a/02-session/Thesaurus.xlsx
+++ b/02-session/Thesaurus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bscl\Desktop\Proyectos 2025\jesus ariel\ADSO-2901817\02-session\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2A34C5-5AB2-43F1-BACF-665068C70F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E65606-5391-4699-A239-B398A476F092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{CBF535E4-71E5-47C2-9BF5-65E8EF8C5F03}"/>
   </bookViews>

--- a/02-session/Thesaurus.xlsx
+++ b/02-session/Thesaurus.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bscl\Desktop\Proyectos 2025\jesus ariel\ADSO-2901817\02-session\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bscl\Desktop\Proyectos_2025\jesus ariel\ADSO-2901817\02-session\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E65606-5391-4699-A239-B398A476F092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A8D02-1129-4375-A57C-F1619CF27434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{CBF535E4-71E5-47C2-9BF5-65E8EF8C5F03}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="345">
   <si>
     <t>Término o Frase</t>
   </si>
@@ -978,11 +978,6 @@
   </si>
   <si>
     <t>Hasta chat GPT y más allá: una breve guía reflexiva sobre el impacto de la Inteligencia Artificial en la educación</t>
-  </si>
-  <si>
-    <t>Una revisión sistemática sobre aula invertida y aprendizaje
-colaborativo apoyados en inteligencia artificial para el aprendizaje
-de programación</t>
   </si>
   <si>
     <t>cómo es el aprendizaje con la inteligencia artificial en programación de software</t>
@@ -1082,6 +1077,12 @@
   </si>
   <si>
     <t>https://www.rade.es/imageslib/PUBLICACIONES/ARTICULOS/V8N3%20-%2001%20-%20ED%20-%20CASAR.pdf</t>
+  </si>
+  <si>
+    <t>https://fesc.edu.co/Revistas/OJS/index.php/mundofesc/article/view/1782/1306</t>
+  </si>
+  <si>
+    <t>Integración de la Inteligencia Artificial en la Enseñanza de la Arquitectura: Impacto en las Competencias de Presupuesto y Programación</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1306,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1460,47 +1461,53 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5277,490 +5284,490 @@
     <col min="3" max="3" width="7.28515625" style="46" customWidth="1"/>
     <col min="4" max="4" width="22.42578125" style="46" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" style="46" customWidth="1"/>
-    <col min="6" max="6" width="55.85546875" style="64" customWidth="1"/>
+    <col min="6" max="6" width="55.85546875" style="58" customWidth="1"/>
     <col min="7" max="7" width="20.140625" style="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="56" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="67" t="s">
         <v>289</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="67" t="s">
         <v>290</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="57" t="s">
         <v>292</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="G1" s="56" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="46" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+    <row r="2" spans="1:7" s="69" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>297</v>
       </c>
-      <c r="C2" s="65">
+      <c r="C2" s="64">
         <v>2021</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="62" t="s">
         <v>298</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="46" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="32">
+    <row r="3" spans="1:7" s="69" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="59" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="4">
         <v>2023</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="70" t="s">
         <v>301</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="G3" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="46" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32">
+    <row r="4" spans="1:7" s="69" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="59" t="s">
         <v>304</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="4">
         <v>2022</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="60" t="s">
         <v>305</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="62" t="s">
         <v>303</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="46" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32">
+    <row r="5" spans="1:7" s="69" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="4">
         <v>2025</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="60" t="s">
         <v>307</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="71" t="s">
         <v>306</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="46" customFormat="1" ht="51" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+    <row r="6" spans="1:7" s="69" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="59" t="s">
         <v>309</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="4">
         <v>2023</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="60" t="s">
         <v>310</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="62" t="s">
         <v>311</v>
       </c>
-      <c r="G6" s="66" t="s">
+      <c r="G6" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="46" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="32">
+    <row r="7" spans="1:7" s="69" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D7" s="60" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="69" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="64">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="65" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="32">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>295</v>
-      </c>
-      <c r="E7" s="67" t="s">
+      <c r="E8" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F8" s="69" t="s">
+        <v>314</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="46" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="59" t="s">
         <v>312</v>
       </c>
-      <c r="G7" s="66" t="s">
+      <c r="C9" s="64">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="65" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>315</v>
+      </c>
+      <c r="G9" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="46" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
-        <v>7</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>313</v>
-      </c>
-      <c r="C8" s="65">
+    <row r="10" spans="1:7" s="46" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2025</v>
+      </c>
+      <c r="D10" s="60" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="F10" s="62" t="s">
+        <v>318</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="69" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="4">
         <v>2023</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>314</v>
-      </c>
-      <c r="E8" s="36" t="s">
+      <c r="D11" s="60" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F8" s="69" t="s">
-        <v>315</v>
-      </c>
-      <c r="G8" s="66" t="s">
+      <c r="F11" s="62" t="s">
+        <v>319</v>
+      </c>
+      <c r="G11" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="46" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="32">
-        <v>8</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>313</v>
-      </c>
-      <c r="C9" s="65">
+    <row r="12" spans="1:7" s="69" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D12" s="60" t="s">
+        <v>322</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>321</v>
+      </c>
+      <c r="G12" s="63" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="69" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="64">
         <v>2023</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="E9" s="36" t="s">
+      <c r="D13" s="65" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F9" s="57" t="s">
-        <v>316</v>
-      </c>
-      <c r="G9" s="66" t="s">
+      <c r="F13" s="63" t="s">
+        <v>323</v>
+      </c>
+      <c r="G13" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="46" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
-        <v>9</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>313</v>
-      </c>
-      <c r="C10" s="32">
-        <v>2025</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="67" t="s">
+    <row r="14" spans="1:7" s="46" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D14" s="66" t="s">
+        <v>325</v>
+      </c>
+      <c r="E14" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F10" s="56" t="s">
-        <v>319</v>
-      </c>
-      <c r="G10" s="66" t="s">
+      <c r="F14" s="62" t="s">
+        <v>326</v>
+      </c>
+      <c r="G14" s="63" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="46" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
-        <v>10</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>313</v>
-      </c>
-      <c r="C11" s="32">
+    <row r="15" spans="1:7" s="69" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D15" s="60" t="s">
+        <v>328</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="69" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>331</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>330</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="69" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="C17" s="64">
         <v>2023</v>
       </c>
-      <c r="D11" s="42" t="s">
-        <v>321</v>
-      </c>
-      <c r="E11" s="67" t="s">
+      <c r="D17" s="65" t="s">
+        <v>333</v>
+      </c>
+      <c r="E17" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F11" s="56" t="s">
-        <v>320</v>
-      </c>
-      <c r="G11" s="66" t="s">
+      <c r="F17" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="G17" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="46" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
-        <v>11</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>313</v>
-      </c>
-      <c r="C12" s="32">
+    <row r="18" spans="1:7" s="69" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="C18" s="64">
+        <v>2023</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>335</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>334</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="69" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="C19" s="64">
         <v>2022</v>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>323</v>
-      </c>
-      <c r="E12" s="67" t="s">
+      <c r="D19" s="65" t="s">
+        <v>337</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F12" s="56" t="s">
-        <v>322</v>
-      </c>
-      <c r="G12" s="66" t="s">
+      <c r="F19" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="G19" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="46" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="32">
-        <v>12</v>
-      </c>
-      <c r="B13" s="59" t="s">
-        <v>313</v>
-      </c>
-      <c r="C13" s="65">
-        <v>2023</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>325</v>
-      </c>
-      <c r="E13" s="36" t="s">
+    <row r="20" spans="1:7" s="69" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="C20" s="64">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F13" s="57" t="s">
-        <v>324</v>
-      </c>
-      <c r="G13" s="36" t="s">
+      <c r="F20" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="G20" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="46" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32">
-        <v>13</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>328</v>
-      </c>
-      <c r="C14" s="32">
-        <v>2019</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="E14" s="67" t="s">
+    <row r="21" spans="1:7" s="69" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="C21" s="64">
+        <v>2022</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>342</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F14" s="56" t="s">
-        <v>327</v>
-      </c>
-      <c r="G14" s="66" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="46" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
-        <v>14</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>328</v>
-      </c>
-      <c r="C15" s="32">
-        <v>2021</v>
-      </c>
-      <c r="D15" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="E15" s="67" t="s">
-        <v>296</v>
-      </c>
-      <c r="F15" s="56" t="s">
-        <v>330</v>
-      </c>
-      <c r="G15" s="66" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="46" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="32">
-        <v>15</v>
-      </c>
-      <c r="B16" s="58" t="s">
-        <v>328</v>
-      </c>
-      <c r="C16" s="32">
-        <v>2024</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="E16" s="67" t="s">
-        <v>296</v>
-      </c>
-      <c r="F16" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="G16" s="66" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="46" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="32">
-        <v>16</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>328</v>
-      </c>
-      <c r="C17" s="65">
-        <v>2023</v>
-      </c>
-      <c r="D17" s="48" t="s">
-        <v>334</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="F17" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="46" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="32">
-        <v>17</v>
-      </c>
-      <c r="B18" s="59" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" s="65">
-        <v>2023</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>336</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="46" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="32">
-        <v>18</v>
-      </c>
-      <c r="B19" s="59" t="s">
-        <v>339</v>
-      </c>
-      <c r="C19" s="65">
-        <v>2022</v>
-      </c>
-      <c r="D19" s="48" t="s">
-        <v>338</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="F19" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="46" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="32">
-        <v>19</v>
-      </c>
-      <c r="B20" s="59" t="s">
-        <v>339</v>
-      </c>
-      <c r="C20" s="65">
-        <v>2022</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>340</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="F20" s="57" t="s">
+      <c r="F21" s="63" t="s">
         <v>341</v>
       </c>
-      <c r="G20" s="36" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="46" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
-        <v>20</v>
-      </c>
-      <c r="B21" s="59" t="s">
-        <v>339</v>
-      </c>
-      <c r="C21" s="65">
-        <v>2022</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>343</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="30" t="s">
         <v>299</v>
       </c>
     </row>
@@ -5933,6 +5940,21 @@
     <hyperlink ref="D9" r:id="rId2" xr:uid="{F74C758A-BB65-49AF-B22A-FB1483180447}"/>
     <hyperlink ref="D18" r:id="rId3" xr:uid="{6F931FA0-B53A-4FD1-A9D2-6E08B1A55A65}"/>
     <hyperlink ref="D19" r:id="rId4" xr:uid="{17C64C2C-8AEA-4787-BD98-1B3F9CE4BF93}"/>
+    <hyperlink ref="D21" r:id="rId5" xr:uid="{0A7E0FBB-37C0-4C1E-BD1A-3DBBFD0F9190}"/>
+    <hyperlink ref="D3" r:id="rId6" xr:uid="{56C7B740-74F8-4FC0-806D-03F5707B1604}"/>
+    <hyperlink ref="D4" r:id="rId7" display="https://d1wqtxts1xzle7.cloudfront.net/105337831/216-libre.pdf?1693228976=&amp;response-content-disposition=inline%3B+filename%3DInteligencia_artificial_en_el_campo_de_l.pdf&amp;Expires=1755359608&amp;Signature=E-2vlB6Tr7-ULqrILRhURhvZ-90F7NiamHyC8wzEuLxKC7cbVuRZQsH-tsp4BrTif9Vas7m6Fwn-qHPDWOHbfEqNxFeScixM5QfmmqyeqxrHN3bp80X5nzvX8hpWyNpDfsFVw8tfsOn6uZhBJMPpAfoj9NqExWxHogFWI~dnhsH-oK16UiH5fxrjxK-TIOrI234LqhhH7zeP4UJlhUfflzQLo18nuaXiPG-sCMQd97TbC8g~LqYeA3mdqVEOrawHgzgsHdGlBSBlH3Ex5LBNcYF6JOAL0ZbQHmLWeqFO9ZfFhL8S5I9tsSCTvtQHB-xy8YlczFnnNfPbil~T3UOl4Q__&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA" xr:uid="{9845B598-4C0A-47FC-A9E0-1A43B6D06536}"/>
+    <hyperlink ref="D5" r:id="rId8" xr:uid="{2E2581F3-96F5-4665-B468-6149148A62BB}"/>
+    <hyperlink ref="D6" r:id="rId9" xr:uid="{A6C67204-85F1-47D3-9D75-9321D919F303}"/>
+    <hyperlink ref="D7" r:id="rId10" xr:uid="{70D5B976-BD25-4ADE-BED3-26BCA5EB2337}"/>
+    <hyperlink ref="D8" r:id="rId11" xr:uid="{2DF661B0-B6C1-49D3-A6BA-5C5B010759DD}"/>
+    <hyperlink ref="D10" r:id="rId12" xr:uid="{0F900A7F-099B-45F4-9514-C3EFEDC254BA}"/>
+    <hyperlink ref="D11" r:id="rId13" xr:uid="{A9EEF2E5-E0F9-4420-883A-434DE87F4B92}"/>
+    <hyperlink ref="D12" r:id="rId14" xr:uid="{6D2D0E50-E86E-4680-87F7-B91BFB9BA01E}"/>
+    <hyperlink ref="D13" r:id="rId15" xr:uid="{4B15811F-EBF1-4DDD-91E2-CDAE72FCF204}"/>
+    <hyperlink ref="D16" r:id="rId16" xr:uid="{68FD9D9A-8701-4FE2-A779-577EE58ACAC8}"/>
+    <hyperlink ref="D15" r:id="rId17" xr:uid="{3C841C08-187B-4D95-8EE9-0BF7494349C6}"/>
+    <hyperlink ref="D17" r:id="rId18" xr:uid="{00413B16-40B6-44EB-923D-CF661C7DA652}"/>
+    <hyperlink ref="D20" r:id="rId19" xr:uid="{E4F1B58E-DB4B-42B8-B1FF-6C45D3D09841}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
